--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/o-higgins.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2832,7 +2832,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4562-44-CM26</t>
+          <t>1499900-20-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,22 +2847,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIAL ORIONIS SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.721.492-6</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1382.62</v>
+        <v>2207.55</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1398-202-CM26</t>
+          <t>4562-44-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3007.61</v>
+        <v>1382.62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4562-72-CM26</t>
+          <t>1398-202-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>561.25</v>
+        <v>3007.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2402-40-CM26</t>
+          <t>4562-72-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>14155.38</v>
+        <v>561.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2401-264-CM26</t>
+          <t>2402-40-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8513.559999999999</v>
+        <v>14155.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4562-157-CM26</t>
+          <t>2401-264-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10801.48</v>
+        <v>8513.559999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2080-2942-CM26</t>
+          <t>4562-157-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1147.05</v>
+        <v>10801.48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2675-118-CM26</t>
+          <t>2080-2942-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,27 +3269,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3632.41</v>
+        <v>1147.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1079563-151-CM26</t>
+          <t>2675-118-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>14144.81</v>
+        <v>3632.41</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4562-244-CM26</t>
+          <t>1079563-151-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.080.300-3</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GRANEROS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6320.27</v>
+        <v>14144.81</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2401-545-CM26</t>
+          <t>4562-244-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.080.300-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7605.35</v>
+        <v>6320.27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2817-299-CM26</t>
+          <t>2401-545-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.090.100-5</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>573.83</v>
+        <v>7605.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3634-288-CM26</t>
+          <t>2817-299-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.090.100-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2662.92</v>
+        <v>573.83</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4371-267-CM26</t>
+          <t>3634-288-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1643.07</v>
+        <v>2662.92</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2675-293-CM26</t>
+          <t>4371-267-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2933.89</v>
+        <v>1643.07</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4371-273-CM26</t>
+          <t>2675-293-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6149.06</v>
+        <v>2933.89</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3181-310-CM26</t>
+          <t>4371-273-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>407.04</v>
+        <v>6149.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2401-698-CM26</t>
+          <t>3181-310-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3889,17 +3889,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3757.1</v>
+        <v>407.04</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2401-699-CM26</t>
+          <t>2401-698-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8396.450000000001</v>
+        <v>3757.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2401-703-CM26</t>
+          <t>2401-699-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2765.01</v>
+        <v>8396.450000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2401-704-CM26</t>
+          <t>554734-431-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.080.900-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE PEUMO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>7339.85</v>
+        <v>3051.14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2401-708-CM26</t>
+          <t>2401-703-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8094.93</v>
+        <v>2765.01</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2568-137-CM26</t>
+          <t>2401-704-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,22 +4189,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4713.11</v>
+        <v>7339.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2675-322-CM26</t>
+          <t>2401-708-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3052.68</v>
+        <v>8094.93</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2776-495-CM26</t>
+          <t>2568-137-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2740.24</v>
+        <v>4713.11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3634-379-CM26</t>
+          <t>2675-322-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,7 +4412,251 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
+        <v>3052.68</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2776-495-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>69.081.200-2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RENGO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>2740.24</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3634-379-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>69.081.500-1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
         <v>3825.65</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4562-506-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.080.300-3</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>2248.08</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4371-417-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>69.081.000-k</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>334.28</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/o-higgins.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/o-higgins.xlsx
@@ -562,7 +562,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2163,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2350,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2415,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2541,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2606,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2858,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2923,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2988,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3053,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3118,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3183,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3248,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3313,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3378,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3504,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3630,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3695,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3760,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3886,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3951,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4016,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4264,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4329,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4516,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4642,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4768,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4833,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/o-higgins.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3968,7 +3968,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4371-273-CM26</t>
+          <t>2401-698-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>69.080.100-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4008,32 +4008,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.029.126-9</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6149.06</v>
+        <v>3757.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3181-310-CM26</t>
+          <t>554734-431-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4053,17 +4049,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>69.080.900-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>I MUNICIPALIDAD DE PEUMO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4073,28 +4069,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>77.798.686-4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>407.04</v>
+        <v>3051.14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2401-698-CM26</t>
+          <t>2401-699-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4149,13 +4149,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3757.1</v>
+        <v>8396.450000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2401-699-CM26</t>
+          <t>3181-310-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4175,17 +4175,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.080.100-0</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8396.450000000001</v>
+        <v>407.04</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>554734-431-CM26</t>
+          <t>4371-273-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.080.900-1</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEUMO</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3051.14</v>
+        <v>6149.06</v>
       </c>
     </row>
     <row r="61">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4845,6 +4845,201 @@
       </c>
       <c r="M69" s="2" t="n">
         <v>334.28</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4562-534-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.080.300-3</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE GRANEROS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>FIMCO SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>77.801.815-2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>9595.98</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2401-992-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.080.100-0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>2577.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2401-995-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.080.100-0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>25538.37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/o-higgins.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/o-higgins.xlsx
@@ -3858,7 +3858,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
